--- a/results/03-2026/beta/inputs-comparison-03-2026.xlsx
+++ b/results/03-2026/beta/inputs-comparison-03-2026.xlsx
@@ -3697,7 +3697,7 @@
         <v>4.222</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.80364</v>
+        <v>2.8036115</v>
       </c>
       <c r="AG20" t="n">
         <v>0.7</v>
@@ -3748,7 +3748,7 @@
         <v>6.35096</v>
       </c>
       <c r="AW20" t="n">
-        <v>8.21888887</v>
+        <v>8.21888317</v>
       </c>
       <c r="AX20" t="n">
         <v>0.4014</v>
@@ -3855,7 +3855,7 @@
         <v>2.372</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.833375</v>
+        <v>2.833394</v>
       </c>
       <c r="AG21" t="n">
         <v>0.7</v>
@@ -3906,7 +3906,7 @@
         <v>4.56094</v>
       </c>
       <c r="AW21" t="n">
-        <v>6.19030152</v>
+        <v>6.190300475</v>
       </c>
       <c r="AX21" t="n">
         <v>0.4023</v>
@@ -4013,7 +4013,7 @@
         <v>2.372</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.823948</v>
+        <v>2.8239574</v>
       </c>
       <c r="AG22" t="n">
         <v>0.7</v>
@@ -4064,7 +4064,7 @@
         <v>3.85754</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.1270965</v>
+        <v>4.12709705</v>
       </c>
       <c r="AX22" t="n">
         <v>0.3861</v>
@@ -4171,7 +4171,7 @@
         <v>2.372</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.865684</v>
+        <v>2.8656558</v>
       </c>
       <c r="AG23" t="n">
         <v>0.7</v>
@@ -4222,7 +4222,7 @@
         <v>3.17264</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.47882573</v>
+        <v>2.478820453</v>
       </c>
       <c r="AX23" t="n">
         <v>0.315</v>
@@ -4329,7 +4329,7 @@
         <v>2.372</v>
       </c>
       <c r="AF24" t="n">
-        <v>-8.089008</v>
+        <v>-8.076788</v>
       </c>
       <c r="AG24" t="n">
         <v>0.7</v>
@@ -4380,7 +4380,7 @@
         <v>2.58402</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.34183368</v>
+        <v>0.344274675</v>
       </c>
       <c r="AX24" t="n">
         <v>0.315</v>
@@ -4538,7 +4538,7 @@
         <v>2.04112</v>
       </c>
       <c r="AW25" t="n">
-        <v>-1.47547052</v>
+        <v>-1.473395937</v>
       </c>
       <c r="AX25" t="n">
         <v>0.315</v>
@@ -4597,7 +4597,7 @@
         <v>75.1961428571429</v>
       </c>
       <c r="P26" t="n">
-        <v>3401.30978935855</v>
+        <v>0.5</v>
       </c>
       <c r="Q26" t="n">
         <v>5098.38692298557</v>
@@ -4696,7 +4696,7 @@
         <v>1.53068</v>
       </c>
       <c r="AW26" t="n">
-        <v>-3.19731131</v>
+        <v>-3.195359969</v>
       </c>
       <c r="AX26" t="n">
         <v>0.28035</v>
@@ -4755,7 +4755,7 @@
         <v>75.1961428571429</v>
       </c>
       <c r="P27" t="n">
-        <v>3433.77518475659</v>
+        <v>0.5</v>
       </c>
       <c r="Q27" t="n">
         <v>5136.57982245723</v>
@@ -4854,7 +4854,7 @@
         <v>1.05376</v>
       </c>
       <c r="AW27" t="n">
-        <v>-4.80902829</v>
+        <v>-4.807197548</v>
       </c>
       <c r="AX27" t="n">
         <v>0.250425</v>
@@ -4913,7 +4913,7 @@
         <v>75.1961428571429</v>
       </c>
       <c r="P28" t="n">
-        <v>3466.99256859914</v>
+        <v>0.5</v>
       </c>
       <c r="Q28" t="n">
         <v>5175.12973428041</v>
@@ -5012,7 +5012,7 @@
         <v>0.61906</v>
       </c>
       <c r="AW28" t="n">
-        <v>-6.37856472</v>
+        <v>-6.3774651</v>
       </c>
       <c r="AX28" t="n">
         <v>0.222075</v>
@@ -5071,7 +5071,7 @@
         <v>75.1961428571429</v>
       </c>
       <c r="P29" t="n">
-        <v>3497.5971870629</v>
+        <v>0.3</v>
       </c>
       <c r="Q29" t="n">
         <v>5209.63879652421</v>
@@ -5170,7 +5170,7 @@
         <v>0.37618</v>
       </c>
       <c r="AW29" t="n">
-        <v>-7.42323798</v>
+        <v>-7.422628014</v>
       </c>
       <c r="AX29" t="n">
         <v>0.1953</v>
@@ -5229,7 +5229,7 @@
         <v>75.1961428571429</v>
       </c>
       <c r="P30" t="n">
-        <v>3529.55305909616</v>
+        <v>0.4</v>
       </c>
       <c r="Q30" t="n">
         <v>5456.24117371526</v>
@@ -5328,7 +5328,7 @@
         <v>0.23798</v>
       </c>
       <c r="AW30" t="n">
-        <v>-8.44170484</v>
+        <v>-8.441094968</v>
       </c>
       <c r="AX30" t="n">
         <v>0.171675</v>
@@ -5387,7 +5387,7 @@
         <v>75.1961428571429</v>
       </c>
       <c r="P31" t="n">
-        <v>3561.43162500994</v>
+        <v>0.5</v>
       </c>
       <c r="Q31" t="n">
         <v>5492.13433341532</v>
@@ -5486,7 +5486,7 @@
         <v>0.11938</v>
       </c>
       <c r="AW31" t="n">
-        <v>-9.32572512</v>
+        <v>-9.32523632</v>
       </c>
       <c r="AX31" t="n">
         <v>0.14805</v>
@@ -5545,7 +5545,7 @@
         <v>75.1961428571429</v>
       </c>
       <c r="P32" t="n">
-        <v>3592.17594462895</v>
+        <v>0.4</v>
       </c>
       <c r="Q32" t="n">
         <v>5528.30528728337</v>
@@ -5703,7 +5703,7 @@
         <v>75.1961428571429</v>
       </c>
       <c r="P33" t="n">
-        <v>3622.79177047259</v>
+        <v>0.4</v>
       </c>
       <c r="Q33" t="n">
         <v>5563.98496925483</v>
@@ -14109,7 +14109,7 @@
         <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.177175</v>
+        <v>0.1771465</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -14160,7 +14160,7 @@
         <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.0354350000000014</v>
+        <v>0.0354293000000006</v>
       </c>
       <c r="AX20" t="n">
         <v>0</v>
@@ -14265,7 +14265,7 @@
         <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.18354</v>
+        <v>0.183559</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -14316,7 +14316,7 @@
         <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.0668277499999999</v>
+        <v>0.0668267049999995</v>
       </c>
       <c r="AX21" t="n">
         <v>0</v>
@@ -14421,7 +14421,7 @@
         <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.178506</v>
+        <v>0.1785154</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -14472,7 +14472,7 @@
         <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.0952510000000002</v>
+        <v>0.0952515499999995</v>
       </c>
       <c r="AX22" t="n">
         <v>0</v>
@@ -14577,7 +14577,7 @@
         <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.196084</v>
+        <v>0.1960558</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -14628,7 +14628,7 @@
         <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.12550547</v>
+        <v>0.125500193</v>
       </c>
       <c r="AX23" t="n">
         <v>0</v>
@@ -14733,7 +14733,7 @@
         <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.217986</v>
+        <v>0.230205999999999</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
         <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.14896919</v>
+        <v>0.151410185</v>
       </c>
       <c r="AX24" t="n">
         <v>0</v>
@@ -14940,7 +14940,7 @@
         <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>0.16598631</v>
+        <v>0.168060893</v>
       </c>
       <c r="AX25" t="n">
         <v>0</v>
@@ -14997,7 +14997,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>-5.24955802703016</v>
+        <v>-3406.05934738558</v>
       </c>
       <c r="Q26" t="n">
         <v>16.0415600829101</v>
@@ -15096,7 +15096,7 @@
         <v>0</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.18981135</v>
+        <v>0.191762691</v>
       </c>
       <c r="AX26" t="n">
         <v>0</v>
@@ -15153,7 +15153,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>-5.29966489395974</v>
+        <v>-3438.57484965055</v>
       </c>
       <c r="Q27" t="n">
         <v>16.3365508267598</v>
@@ -15252,7 +15252,7 @@
         <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.21663816</v>
+        <v>0.218468902</v>
       </c>
       <c r="AX27" t="n">
         <v>0</v>
@@ -15309,7 +15309,7 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>-5.35093237465981</v>
+        <v>-3471.8435009738</v>
       </c>
       <c r="Q28" t="n">
         <v>16.6352516922598</v>
@@ -15408,7 +15408,7 @@
         <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.17290004</v>
+        <v>0.17399966</v>
       </c>
       <c r="AX28" t="n">
         <v>0</v>
@@ -15465,7 +15465,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>-5.39816733133011</v>
+        <v>-3502.69535439423</v>
       </c>
       <c r="Q29" t="n">
         <v>16.8907114519898</v>
@@ -15564,7 +15564,7 @@
         <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.13579804</v>
+        <v>0.136408006</v>
       </c>
       <c r="AX29" t="n">
         <v>0</v>
@@ -15621,7 +15621,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>-5.44748780343025</v>
+        <v>-3534.60054689959</v>
       </c>
       <c r="Q30" t="n">
         <v>16.2098050751702</v>
@@ -15720,7 +15720,7 @@
         <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.0987742600000008</v>
+        <v>0.0993841320000008</v>
       </c>
       <c r="AX30" t="n">
         <v>0</v>
@@ -15777,7 +15777,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>-5.49668896178991</v>
+        <v>-3566.42831397173</v>
       </c>
       <c r="Q31" t="n">
         <v>16.4672186022699</v>
@@ -15876,7 +15876,7 @@
         <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.0602220400000011</v>
+        <v>0.0607108400000005</v>
       </c>
       <c r="AX31" t="n">
         <v>0</v>
@@ -15933,7 +15933,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>-5.54413953225958</v>
+        <v>-3597.32008416121</v>
       </c>
       <c r="Q32" t="n">
         <v>16.7275046211098</v>
@@ -16089,7 +16089,7 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>-5.59139178631995</v>
+        <v>-3627.98316225891</v>
       </c>
       <c r="Q33" t="n">
         <v>16.9872739017492</v>
